--- a/artfynd/A 3446-2026 artfynd.xlsx
+++ b/artfynd/A 3446-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131870917</v>
       </c>
       <c r="B2" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131870933</v>
       </c>
       <c r="B3" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>131870875</v>
       </c>
       <c r="B4" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 3446-2026 artfynd.xlsx
+++ b/artfynd/A 3446-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131870917</v>
       </c>
       <c r="B2" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131870933</v>
       </c>
       <c r="B3" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>131870875</v>
       </c>
       <c r="B4" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 3446-2026 artfynd.xlsx
+++ b/artfynd/A 3446-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131870917</v>
       </c>
       <c r="B2" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131870933</v>
       </c>
       <c r="B3" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>131870875</v>
       </c>
       <c r="B4" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 3446-2026 artfynd.xlsx
+++ b/artfynd/A 3446-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131870917</v>
       </c>
       <c r="B2" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131870933</v>
       </c>
       <c r="B3" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>131870875</v>
       </c>
       <c r="B4" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 3446-2026 artfynd.xlsx
+++ b/artfynd/A 3446-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131870917</v>
       </c>
       <c r="B2" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131870933</v>
       </c>
       <c r="B3" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>131870875</v>
       </c>
       <c r="B4" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 3446-2026 artfynd.xlsx
+++ b/artfynd/A 3446-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131870917</v>
+        <v>119260787</v>
       </c>
       <c r="B2" t="n">
-        <v>57949</v>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>772382</v>
+        <v>772429</v>
       </c>
       <c r="R2" t="n">
-        <v>7190640</v>
+        <v>7190573</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,47 +743,43 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131870933</v>
+        <v>119260783</v>
       </c>
       <c r="B3" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,7 +809,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -828,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772404</v>
+        <v>772429</v>
       </c>
       <c r="R3" t="n">
-        <v>7190604</v>
+        <v>7190573</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,24 +849,24 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>barksprätt</t>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -883,22 +874,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131870875</v>
+        <v>131832194</v>
       </c>
       <c r="B4" t="n">
-        <v>57949</v>
+        <v>57975</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,17 +925,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Klutmarksberget, Vb</t>
+          <t>Klutmark, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>772361</v>
+        <v>772429</v>
       </c>
       <c r="R4" t="n">
-        <v>7190630</v>
+        <v>7190606</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,24 +959,24 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>Födosök på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -993,15 +984,777 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131870875</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Klutmarksberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>772361</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7190630</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Patrik Nygren</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Patrik Nygren</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131870917</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Klutmarksberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>772382</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7190640</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131870933</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Klutmarksberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>772404</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7190604</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>barksprätt</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131870939</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Klutmarksberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>772432</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7190626</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131870963</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Klutmarksberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>772434</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7190618</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131870998</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Klutmarksberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>772443</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7190582</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131832132</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Klutmark, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>772338</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7190629</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3446-2026 artfynd.xlsx
+++ b/artfynd/A 3446-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119260787</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119260783</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131832194</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,6 +1123,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131870875</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1213,6 +1238,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131870917</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1323,6 +1353,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131870933</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1433,6 +1468,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131870939</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1543,6 +1583,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131870963</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1653,6 +1698,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131870998</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1755,8 +1805,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131832132</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>